--- a/outputs/Beans_(fava,_dry)_percentile_classification_matrix.xlsx
+++ b/outputs/Beans_(fava,_dry)_percentile_classification_matrix.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2128" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2128" uniqueCount="119">
   <si>
     <t>2020 Mar</t>
   </si>
@@ -326,6 +326,9 @@
   </si>
   <si>
     <t>Minimal</t>
+  </si>
+  <si>
+    <t>No data</t>
   </si>
   <si>
     <t>Alert</t>
@@ -988,10 +991,10 @@
         <v>103</v>
       </c>
       <c r="C2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E2" t="s">
         <v>103</v>
@@ -1003,22 +1006,22 @@
         <v>103</v>
       </c>
       <c r="H2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I2" t="s">
         <v>103</v>
       </c>
       <c r="J2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N2" t="s">
         <v>103</v>
@@ -1030,7 +1033,7 @@
         <v>103</v>
       </c>
       <c r="Q2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="R2" t="s">
         <v>103</v>
@@ -1048,7 +1051,7 @@
         <v>103</v>
       </c>
       <c r="W2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="X2" t="s">
         <v>103</v>
@@ -1057,157 +1060,157 @@
         <v>103</v>
       </c>
       <c r="Z2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AA2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AB2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AC2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AD2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AE2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AF2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AG2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AH2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AI2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AJ2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AL2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AM2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AN2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AO2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AP2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AQ2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AR2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AS2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AT2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AU2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AV2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AW2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AX2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AY2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AZ2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BA2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BB2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BC2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BD2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BE2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BF2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BG2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BH2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BI2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BJ2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BK2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BL2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BM2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BN2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BO2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BP2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BQ2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BR2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BS2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BT2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BU2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BV2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="BW2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="BX2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="3" spans="1:76">
@@ -1215,154 +1218,154 @@
         <v>77</v>
       </c>
       <c r="B3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="O3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="P3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Q3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="R3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="S3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="T3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="U3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="V3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="W3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="X3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Y3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Z3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AA3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AB3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AC3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AD3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AE3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AF3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AG3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AH3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AI3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AJ3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AL3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AM3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AN3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AO3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AP3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AQ3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AR3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AS3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AT3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AU3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AV3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AW3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AX3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AY3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AZ3" t="s">
         <v>103</v>
@@ -1371,73 +1374,73 @@
         <v>103</v>
       </c>
       <c r="BB3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BC3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BD3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BE3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BF3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BG3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BH3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BI3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BJ3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BK3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BL3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BM3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BN3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BO3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BP3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BQ3" t="s">
         <v>103</v>
       </c>
       <c r="BR3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BS3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BT3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BU3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BV3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="BW3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="BX3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="4" spans="1:76">
@@ -1451,7 +1454,7 @@
         <v>103</v>
       </c>
       <c r="D4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E4" t="s">
         <v>103</v>
@@ -1460,7 +1463,7 @@
         <v>103</v>
       </c>
       <c r="G4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H4" t="s">
         <v>103</v>
@@ -1484,16 +1487,16 @@
         <v>103</v>
       </c>
       <c r="O4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="P4" t="s">
         <v>103</v>
       </c>
       <c r="Q4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="R4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="S4" t="s">
         <v>103</v>
@@ -1514,13 +1517,13 @@
         <v>103</v>
       </c>
       <c r="Y4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Z4" t="s">
         <v>103</v>
       </c>
       <c r="AA4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AB4" t="s">
         <v>103</v>
@@ -1532,7 +1535,7 @@
         <v>103</v>
       </c>
       <c r="AE4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AF4" t="s">
         <v>103</v>
@@ -1544,10 +1547,10 @@
         <v>103</v>
       </c>
       <c r="AI4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AJ4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK4" t="s">
         <v>103</v>
@@ -1559,22 +1562,22 @@
         <v>103</v>
       </c>
       <c r="AN4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AO4" t="s">
         <v>103</v>
       </c>
       <c r="AP4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AQ4" t="s">
         <v>103</v>
       </c>
       <c r="AR4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AS4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AT4" t="s">
         <v>103</v>
@@ -1589,85 +1592,85 @@
         <v>103</v>
       </c>
       <c r="AX4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AY4" t="s">
         <v>103</v>
       </c>
       <c r="AZ4" t="s">
+        <v>106</v>
+      </c>
+      <c r="BA4" t="s">
+        <v>104</v>
+      </c>
+      <c r="BB4" t="s">
+        <v>104</v>
+      </c>
+      <c r="BC4" t="s">
+        <v>103</v>
+      </c>
+      <c r="BD4" t="s">
+        <v>106</v>
+      </c>
+      <c r="BE4" t="s">
         <v>105</v>
       </c>
-      <c r="BA4" t="s">
-        <v>103</v>
-      </c>
-      <c r="BB4" t="s">
-        <v>103</v>
-      </c>
-      <c r="BC4" t="s">
-        <v>103</v>
-      </c>
-      <c r="BD4" t="s">
+      <c r="BF4" t="s">
+        <v>104</v>
+      </c>
+      <c r="BG4" t="s">
+        <v>106</v>
+      </c>
+      <c r="BH4" t="s">
+        <v>104</v>
+      </c>
+      <c r="BI4" t="s">
+        <v>104</v>
+      </c>
+      <c r="BJ4" t="s">
+        <v>104</v>
+      </c>
+      <c r="BK4" t="s">
+        <v>104</v>
+      </c>
+      <c r="BL4" t="s">
+        <v>104</v>
+      </c>
+      <c r="BM4" t="s">
+        <v>106</v>
+      </c>
+      <c r="BN4" t="s">
+        <v>106</v>
+      </c>
+      <c r="BO4" t="s">
+        <v>103</v>
+      </c>
+      <c r="BP4" t="s">
+        <v>106</v>
+      </c>
+      <c r="BQ4" t="s">
+        <v>106</v>
+      </c>
+      <c r="BR4" t="s">
+        <v>104</v>
+      </c>
+      <c r="BS4" t="s">
+        <v>104</v>
+      </c>
+      <c r="BT4" t="s">
         <v>105</v>
       </c>
-      <c r="BE4" t="s">
-        <v>104</v>
-      </c>
-      <c r="BF4" t="s">
-        <v>103</v>
-      </c>
-      <c r="BG4" t="s">
-        <v>105</v>
-      </c>
-      <c r="BH4" t="s">
-        <v>103</v>
-      </c>
-      <c r="BI4" t="s">
-        <v>103</v>
-      </c>
-      <c r="BJ4" t="s">
-        <v>103</v>
-      </c>
-      <c r="BK4" t="s">
-        <v>103</v>
-      </c>
-      <c r="BL4" t="s">
-        <v>103</v>
-      </c>
-      <c r="BM4" t="s">
-        <v>105</v>
-      </c>
-      <c r="BN4" t="s">
-        <v>105</v>
-      </c>
-      <c r="BO4" t="s">
-        <v>103</v>
-      </c>
-      <c r="BP4" t="s">
-        <v>105</v>
-      </c>
-      <c r="BQ4" t="s">
-        <v>105</v>
-      </c>
-      <c r="BR4" t="s">
-        <v>103</v>
-      </c>
-      <c r="BS4" t="s">
-        <v>103</v>
-      </c>
-      <c r="BT4" t="s">
-        <v>104</v>
-      </c>
       <c r="BU4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="BV4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="BW4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="BX4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="5" spans="1:76">
@@ -1675,55 +1678,55 @@
         <v>79</v>
       </c>
       <c r="B5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="O5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="P5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Q5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="R5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="S5" t="s">
         <v>103</v>
@@ -1735,7 +1738,7 @@
         <v>103</v>
       </c>
       <c r="V5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="W5" t="s">
         <v>103</v>
@@ -1753,25 +1756,25 @@
         <v>103</v>
       </c>
       <c r="AB5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AC5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AD5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AE5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AF5" t="s">
         <v>103</v>
       </c>
       <c r="AG5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AH5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AI5" t="s">
         <v>103</v>
@@ -1780,7 +1783,7 @@
         <v>103</v>
       </c>
       <c r="AK5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AL5" t="s">
         <v>103</v>
@@ -1789,7 +1792,7 @@
         <v>103</v>
       </c>
       <c r="AN5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AO5" t="s">
         <v>103</v>
@@ -1816,28 +1819,28 @@
         <v>103</v>
       </c>
       <c r="AW5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AX5" t="s">
         <v>103</v>
       </c>
       <c r="AY5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AZ5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BA5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BB5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BC5" t="s">
         <v>103</v>
       </c>
       <c r="BD5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="BE5" t="s">
         <v>103</v>
@@ -1846,19 +1849,19 @@
         <v>103</v>
       </c>
       <c r="BG5" t="s">
+        <v>106</v>
+      </c>
+      <c r="BH5" t="s">
+        <v>106</v>
+      </c>
+      <c r="BI5" t="s">
+        <v>103</v>
+      </c>
+      <c r="BJ5" t="s">
         <v>105</v>
       </c>
-      <c r="BH5" t="s">
-        <v>105</v>
-      </c>
-      <c r="BI5" t="s">
-        <v>103</v>
-      </c>
-      <c r="BJ5" t="s">
-        <v>104</v>
-      </c>
       <c r="BK5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BL5" t="s">
         <v>103</v>
@@ -1873,7 +1876,7 @@
         <v>103</v>
       </c>
       <c r="BP5" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="BQ5" t="s">
         <v>103</v>
@@ -1882,22 +1885,22 @@
         <v>103</v>
       </c>
       <c r="BS5" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="BT5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BU5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BV5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BW5" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="BX5" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="6" spans="1:76">
@@ -1905,55 +1908,55 @@
         <v>80</v>
       </c>
       <c r="B6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="O6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="P6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Q6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="R6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="S6" t="s">
         <v>103</v>
@@ -1962,10 +1965,10 @@
         <v>103</v>
       </c>
       <c r="U6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="V6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="W6" t="s">
         <v>103</v>
@@ -1974,19 +1977,19 @@
         <v>103</v>
       </c>
       <c r="Y6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Z6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AA6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AB6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AC6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AD6" t="s">
         <v>103</v>
@@ -1995,28 +1998,28 @@
         <v>103</v>
       </c>
       <c r="AF6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AG6" t="s">
         <v>103</v>
       </c>
       <c r="AH6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AI6" t="s">
         <v>103</v>
       </c>
       <c r="AJ6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK6" t="s">
         <v>103</v>
       </c>
       <c r="AL6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AM6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AN6" t="s">
         <v>103</v>
@@ -2040,7 +2043,7 @@
         <v>103</v>
       </c>
       <c r="AU6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AV6" t="s">
         <v>103</v>
@@ -2061,73 +2064,73 @@
         <v>103</v>
       </c>
       <c r="BB6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="BC6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="BD6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="BE6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="BF6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BG6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="BH6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="BI6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="BJ6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BK6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BL6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BM6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BN6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BO6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BP6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BQ6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BR6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BS6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BT6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BU6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BV6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="BW6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="BX6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="7" spans="1:76">
@@ -2135,202 +2138,202 @@
         <v>81</v>
       </c>
       <c r="B7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="O7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="P7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Q7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="R7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="S7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="T7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="U7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="V7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="W7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="X7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Y7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Z7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AA7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AB7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AC7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AD7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AE7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AF7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AG7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AH7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AI7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AJ7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AL7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AM7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AN7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AO7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AP7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AQ7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AR7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AS7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AT7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AU7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AV7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AW7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AX7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AY7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AZ7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BA7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BB7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BC7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BD7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BE7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BF7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BG7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BH7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BI7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BJ7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BK7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BL7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BM7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BN7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BO7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BP7" t="s">
         <v>103</v>
@@ -2339,25 +2342,25 @@
         <v>103</v>
       </c>
       <c r="BR7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BS7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BT7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BU7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BV7" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="BW7" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="BX7" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="8" spans="1:76">
@@ -2365,55 +2368,55 @@
         <v>82</v>
       </c>
       <c r="B8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="O8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="P8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Q8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="R8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="S8" t="s">
         <v>103</v>
@@ -2425,7 +2428,7 @@
         <v>103</v>
       </c>
       <c r="V8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="W8" t="s">
         <v>103</v>
@@ -2437,7 +2440,7 @@
         <v>103</v>
       </c>
       <c r="Z8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AA8" t="s">
         <v>103</v>
@@ -2452,7 +2455,7 @@
         <v>103</v>
       </c>
       <c r="AE8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AF8" t="s">
         <v>103</v>
@@ -2470,7 +2473,7 @@
         <v>103</v>
       </c>
       <c r="AK8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AL8" t="s">
         <v>103</v>
@@ -2479,115 +2482,115 @@
         <v>103</v>
       </c>
       <c r="AN8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AO8" t="s">
         <v>103</v>
       </c>
       <c r="AP8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AQ8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AR8" t="s">
         <v>103</v>
       </c>
       <c r="AS8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AT8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AU8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AV8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AW8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AX8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AY8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AZ8" t="s">
         <v>103</v>
       </c>
       <c r="BA8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BB8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BC8" t="s">
         <v>103</v>
       </c>
       <c r="BD8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BE8" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="BF8" t="s">
         <v>103</v>
       </c>
       <c r="BG8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BH8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BI8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BJ8" t="s">
         <v>103</v>
       </c>
       <c r="BK8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BL8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BM8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BN8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BO8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BP8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BQ8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BR8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BS8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BT8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BU8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BV8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="BW8" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="BX8" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="9" spans="1:76">
@@ -2595,28 +2598,28 @@
         <v>83</v>
       </c>
       <c r="B9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H9" t="s">
         <v>103</v>
       </c>
       <c r="I9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J9" t="s">
         <v>103</v>
@@ -2637,16 +2640,16 @@
         <v>103</v>
       </c>
       <c r="P9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Q9" t="s">
         <v>103</v>
       </c>
       <c r="R9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="S9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="T9" t="s">
         <v>103</v>
@@ -2658,16 +2661,16 @@
         <v>103</v>
       </c>
       <c r="W9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="X9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Y9" t="s">
         <v>103</v>
       </c>
       <c r="Z9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AA9" t="s">
         <v>103</v>
@@ -2676,148 +2679,148 @@
         <v>103</v>
       </c>
       <c r="AC9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AD9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AE9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AF9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AG9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AH9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AI9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AJ9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AL9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AM9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AN9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AO9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AP9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AQ9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AR9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AS9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AT9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AU9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AV9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AW9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AX9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AY9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AZ9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BA9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BB9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BC9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BD9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BE9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BF9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BG9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BH9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BI9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BJ9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BK9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BL9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BM9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BN9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BO9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BP9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BQ9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BR9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BS9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BT9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BU9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BV9" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="BW9" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="BX9" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="10" spans="1:76">
@@ -2825,106 +2828,106 @@
         <v>84</v>
       </c>
       <c r="B10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="O10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="P10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Q10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="R10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="S10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="T10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="U10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="V10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="W10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="X10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Y10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Z10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AA10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AB10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AC10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AD10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AE10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AF10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AG10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AH10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AI10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AJ10" t="s">
         <v>103</v>
@@ -2936,7 +2939,7 @@
         <v>103</v>
       </c>
       <c r="AM10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AN10" t="s">
         <v>103</v>
@@ -2960,7 +2963,7 @@
         <v>103</v>
       </c>
       <c r="AU10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AV10" t="s">
         <v>103</v>
@@ -2972,82 +2975,82 @@
         <v>103</v>
       </c>
       <c r="AY10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AZ10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BA10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BB10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BC10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BD10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BE10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BF10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BG10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BH10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BI10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BJ10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BK10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BL10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BM10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BN10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BO10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BP10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BQ10" t="s">
         <v>103</v>
       </c>
       <c r="BR10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BS10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BT10" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="BU10" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="BV10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="BW10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="BX10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="11" spans="1:76">
@@ -3055,205 +3058,205 @@
         <v>85</v>
       </c>
       <c r="B11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="O11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="P11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Q11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="R11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="S11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="T11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="U11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="V11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="W11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="X11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Y11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Z11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AA11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AB11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AC11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AD11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AE11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AF11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AG11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AH11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AI11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AJ11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AL11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AM11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AN11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AO11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AP11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AQ11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AR11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AS11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AT11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AU11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AV11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AW11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AX11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AY11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AZ11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BA11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BB11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BC11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BD11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BE11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BF11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BG11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BH11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BI11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BJ11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BK11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BL11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BM11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BN11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BO11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BP11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BQ11" t="s">
         <v>103</v>
@@ -3262,22 +3265,22 @@
         <v>103</v>
       </c>
       <c r="BS11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BT11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BU11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BV11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="BW11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="BX11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="12" spans="1:76">
@@ -3285,229 +3288,229 @@
         <v>86</v>
       </c>
       <c r="B12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="O12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="P12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Q12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="R12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="S12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="T12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="U12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="V12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="W12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="X12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Y12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Z12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AA12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AB12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AC12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AD12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AE12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AF12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AG12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AH12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AI12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AJ12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AL12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AM12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AN12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AO12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AP12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AQ12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AR12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AS12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AT12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AU12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AV12" t="s">
         <v>103</v>
       </c>
       <c r="AW12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AX12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AY12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AZ12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BA12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BB12" t="s">
         <v>103</v>
       </c>
       <c r="BC12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BD12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BE12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BF12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BG12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BH12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BI12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BJ12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BK12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BL12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BM12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BN12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BO12" t="s">
         <v>103</v>
       </c>
       <c r="BP12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BQ12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BR12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BS12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BT12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BU12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BV12" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="BW12" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="BX12" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="13" spans="1:76">
@@ -3515,7 +3518,7 @@
         <v>87</v>
       </c>
       <c r="B13" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C13" t="s">
         <v>103</v>
@@ -3527,7 +3530,7 @@
         <v>103</v>
       </c>
       <c r="F13" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G13" t="s">
         <v>103</v>
@@ -3542,13 +3545,13 @@
         <v>103</v>
       </c>
       <c r="K13" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L13" t="s">
         <v>103</v>
       </c>
       <c r="M13" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N13" t="s">
         <v>103</v>
@@ -3566,7 +3569,7 @@
         <v>103</v>
       </c>
       <c r="S13" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="T13" t="s">
         <v>103</v>
@@ -3578,19 +3581,19 @@
         <v>103</v>
       </c>
       <c r="W13" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="X13" t="s">
         <v>103</v>
       </c>
       <c r="Y13" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Z13" t="s">
         <v>103</v>
       </c>
       <c r="AA13" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AB13" t="s">
         <v>103</v>
@@ -3599,7 +3602,7 @@
         <v>103</v>
       </c>
       <c r="AD13" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AE13" t="s">
         <v>103</v>
@@ -3611,13 +3614,13 @@
         <v>103</v>
       </c>
       <c r="AH13" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AI13" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AJ13" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK13" t="s">
         <v>103</v>
@@ -3641,10 +3644,10 @@
         <v>103</v>
       </c>
       <c r="AR13" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AS13" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AT13" t="s">
         <v>103</v>
@@ -3665,79 +3668,79 @@
         <v>103</v>
       </c>
       <c r="AZ13" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="BA13" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BB13" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="BC13" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="BD13" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BE13" t="s">
+        <v>106</v>
+      </c>
+      <c r="BF13" t="s">
         <v>105</v>
       </c>
-      <c r="BF13" t="s">
-        <v>104</v>
-      </c>
       <c r="BG13" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BH13" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="BI13" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="BJ13" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="BK13" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="BL13" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="BM13" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="BN13" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BO13" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="BP13" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BQ13" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="BR13" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="BS13" t="s">
         <v>103</v>
       </c>
       <c r="BT13" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BU13" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BV13" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="BW13" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BX13" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="14" spans="1:76">
@@ -3757,28 +3760,28 @@
         <v>103</v>
       </c>
       <c r="F14" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G14" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H14" t="s">
         <v>103</v>
       </c>
       <c r="I14" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J14" t="s">
         <v>103</v>
       </c>
       <c r="K14" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L14" t="s">
         <v>103</v>
       </c>
       <c r="M14" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N14" t="s">
         <v>103</v>
@@ -3787,7 +3790,7 @@
         <v>103</v>
       </c>
       <c r="P14" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Q14" t="s">
         <v>103</v>
@@ -3805,7 +3808,7 @@
         <v>103</v>
       </c>
       <c r="V14" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="W14" t="s">
         <v>103</v>
@@ -3814,19 +3817,19 @@
         <v>103</v>
       </c>
       <c r="Y14" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Z14" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AA14" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AB14" t="s">
         <v>103</v>
       </c>
       <c r="AC14" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AD14" t="s">
         <v>103</v>
@@ -3838,7 +3841,7 @@
         <v>103</v>
       </c>
       <c r="AG14" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AH14" t="s">
         <v>103</v>
@@ -3847,19 +3850,19 @@
         <v>103</v>
       </c>
       <c r="AJ14" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK14" t="s">
         <v>103</v>
       </c>
       <c r="AL14" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AM14" t="s">
         <v>103</v>
       </c>
       <c r="AN14" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AO14" t="s">
         <v>103</v>
@@ -3871,10 +3874,10 @@
         <v>103</v>
       </c>
       <c r="AR14" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AS14" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AT14" t="s">
         <v>103</v>
@@ -3892,7 +3895,7 @@
         <v>103</v>
       </c>
       <c r="AY14" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AZ14" t="s">
         <v>103</v>
@@ -3901,14 +3904,14 @@
         <v>103</v>
       </c>
       <c r="BB14" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="BC14" t="s">
+        <v>106</v>
+      </c>
+      <c r="BD14" t="s">
         <v>105</v>
       </c>
-      <c r="BD14" t="s">
-        <v>104</v>
-      </c>
       <c r="BE14" t="s">
         <v>103</v>
       </c>
@@ -3916,10 +3919,10 @@
         <v>103</v>
       </c>
       <c r="BG14" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BH14" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="BI14" t="s">
         <v>103</v>
@@ -3928,46 +3931,46 @@
         <v>103</v>
       </c>
       <c r="BK14" t="s">
+        <v>106</v>
+      </c>
+      <c r="BL14" t="s">
+        <v>103</v>
+      </c>
+      <c r="BM14" t="s">
         <v>105</v>
       </c>
-      <c r="BL14" t="s">
-        <v>103</v>
-      </c>
-      <c r="BM14" t="s">
-        <v>104</v>
-      </c>
       <c r="BN14" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="BO14" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="BP14" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="BQ14" t="s">
         <v>103</v>
       </c>
       <c r="BR14" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="BS14" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="BT14" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="BU14" t="s">
         <v>103</v>
       </c>
       <c r="BV14" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="BW14" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BX14" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="15" spans="1:76">
@@ -3975,7 +3978,7 @@
         <v>89</v>
       </c>
       <c r="B15" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C15" t="s">
         <v>103</v>
@@ -3984,19 +3987,19 @@
         <v>103</v>
       </c>
       <c r="E15" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F15" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G15" t="s">
         <v>103</v>
       </c>
       <c r="H15" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I15" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J15" t="s">
         <v>103</v>
@@ -4011,19 +4014,19 @@
         <v>103</v>
       </c>
       <c r="N15" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="O15" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="P15" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Q15" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="R15" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="S15" t="s">
         <v>103</v>
@@ -4032,52 +4035,52 @@
         <v>103</v>
       </c>
       <c r="U15" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="V15" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="W15" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="X15" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Y15" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Z15" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AA15" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AB15" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AC15" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AD15" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AE15" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AF15" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AG15" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AH15" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AI15" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AJ15" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK15" t="s">
         <v>103</v>
@@ -4086,64 +4089,64 @@
         <v>103</v>
       </c>
       <c r="AM15" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AN15" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AO15" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AP15" t="s">
         <v>103</v>
       </c>
       <c r="AQ15" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AR15" t="s">
         <v>103</v>
       </c>
       <c r="AS15" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AT15" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AU15" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AV15" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AW15" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AX15" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AY15" t="s">
         <v>103</v>
       </c>
       <c r="AZ15" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BA15" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BB15" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BC15" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BD15" t="s">
         <v>103</v>
       </c>
       <c r="BE15" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BF15" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BG15" t="s">
         <v>103</v>
@@ -4152,25 +4155,25 @@
         <v>103</v>
       </c>
       <c r="BI15" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BJ15" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BK15" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BL15" t="s">
         <v>103</v>
       </c>
       <c r="BM15" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BN15" t="s">
         <v>103</v>
       </c>
       <c r="BO15" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BP15" t="s">
         <v>103</v>
@@ -4179,25 +4182,25 @@
         <v>103</v>
       </c>
       <c r="BR15" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BS15" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BT15" t="s">
         <v>103</v>
       </c>
       <c r="BU15" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BV15" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="BW15" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="BX15" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="16" spans="1:76">
@@ -4208,7 +4211,7 @@
         <v>103</v>
       </c>
       <c r="C16" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D16" t="s">
         <v>103</v>
@@ -4220,7 +4223,7 @@
         <v>103</v>
       </c>
       <c r="G16" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H16" t="s">
         <v>103</v>
@@ -4229,7 +4232,7 @@
         <v>103</v>
       </c>
       <c r="J16" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K16" t="s">
         <v>103</v>
@@ -4238,10 +4241,10 @@
         <v>103</v>
       </c>
       <c r="M16" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N16" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="O16" t="s">
         <v>103</v>
@@ -4250,19 +4253,19 @@
         <v>103</v>
       </c>
       <c r="Q16" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="R16" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="S16" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="T16" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="U16" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="V16" t="s">
         <v>103</v>
@@ -4286,10 +4289,10 @@
         <v>103</v>
       </c>
       <c r="AC16" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AD16" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AE16" t="s">
         <v>103</v>
@@ -4310,7 +4313,7 @@
         <v>103</v>
       </c>
       <c r="AK16" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AL16" t="s">
         <v>103</v>
@@ -4322,10 +4325,10 @@
         <v>103</v>
       </c>
       <c r="AO16" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AP16" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AQ16" t="s">
         <v>103</v>
@@ -4334,10 +4337,10 @@
         <v>103</v>
       </c>
       <c r="AS16" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AT16" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AU16" t="s">
         <v>103</v>
@@ -4346,88 +4349,88 @@
         <v>103</v>
       </c>
       <c r="AW16" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AX16" t="s">
         <v>103</v>
       </c>
       <c r="AY16" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AZ16" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BA16" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BB16" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BC16" t="s">
         <v>103</v>
       </c>
       <c r="BD16" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="BE16" t="s">
         <v>103</v>
       </c>
       <c r="BF16" t="s">
+        <v>106</v>
+      </c>
+      <c r="BG16" t="s">
+        <v>106</v>
+      </c>
+      <c r="BH16" t="s">
+        <v>104</v>
+      </c>
+      <c r="BI16" t="s">
+        <v>103</v>
+      </c>
+      <c r="BJ16" t="s">
+        <v>104</v>
+      </c>
+      <c r="BK16" t="s">
+        <v>106</v>
+      </c>
+      <c r="BL16" t="s">
+        <v>106</v>
+      </c>
+      <c r="BM16" t="s">
+        <v>104</v>
+      </c>
+      <c r="BN16" t="s">
+        <v>104</v>
+      </c>
+      <c r="BO16" t="s">
         <v>105</v>
       </c>
-      <c r="BG16" t="s">
-        <v>105</v>
-      </c>
-      <c r="BH16" t="s">
-        <v>103</v>
-      </c>
-      <c r="BI16" t="s">
-        <v>103</v>
-      </c>
-      <c r="BJ16" t="s">
-        <v>103</v>
-      </c>
-      <c r="BK16" t="s">
-        <v>105</v>
-      </c>
-      <c r="BL16" t="s">
-        <v>105</v>
-      </c>
-      <c r="BM16" t="s">
-        <v>103</v>
-      </c>
-      <c r="BN16" t="s">
-        <v>103</v>
-      </c>
-      <c r="BO16" t="s">
-        <v>104</v>
-      </c>
       <c r="BP16" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BQ16" t="s">
         <v>103</v>
       </c>
       <c r="BR16" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BS16" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="BT16" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BU16" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BV16" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BW16" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="BX16" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="17" spans="1:76">
@@ -4435,16 +4438,16 @@
         <v>91</v>
       </c>
       <c r="B17" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C17" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D17" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E17" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F17" t="s">
         <v>103</v>
@@ -4456,40 +4459,40 @@
         <v>103</v>
       </c>
       <c r="I17" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J17" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K17" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L17" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M17" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N17" t="s">
         <v>103</v>
       </c>
       <c r="O17" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="P17" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Q17" t="s">
         <v>103</v>
       </c>
       <c r="R17" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="S17" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="T17" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="U17" t="s">
         <v>103</v>
@@ -4504,16 +4507,16 @@
         <v>103</v>
       </c>
       <c r="Y17" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Z17" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AA17" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AB17" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AC17" t="s">
         <v>103</v>
@@ -4522,22 +4525,22 @@
         <v>103</v>
       </c>
       <c r="AE17" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AF17" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AG17" t="s">
         <v>103</v>
       </c>
       <c r="AH17" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AI17" t="s">
         <v>103</v>
       </c>
       <c r="AJ17" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK17" t="s">
         <v>103</v>
@@ -4546,25 +4549,25 @@
         <v>103</v>
       </c>
       <c r="AM17" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AN17" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AO17" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AP17" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AQ17" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AR17" t="s">
         <v>103</v>
       </c>
       <c r="AS17" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AT17" t="s">
         <v>103</v>
@@ -4573,91 +4576,91 @@
         <v>103</v>
       </c>
       <c r="AV17" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AW17" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AX17" t="s">
         <v>103</v>
       </c>
       <c r="AY17" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AZ17" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BA17" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BB17" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BC17" t="s">
         <v>103</v>
       </c>
       <c r="BD17" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BE17" t="s">
         <v>103</v>
       </c>
       <c r="BF17" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="BG17" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="BH17" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BI17" t="s">
         <v>103</v>
       </c>
       <c r="BJ17" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="BK17" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BL17" t="s">
         <v>103</v>
       </c>
       <c r="BM17" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="BN17" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BO17" t="s">
         <v>103</v>
       </c>
       <c r="BP17" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BQ17" t="s">
         <v>103</v>
       </c>
       <c r="BR17" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BS17" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="BT17" t="s">
         <v>103</v>
       </c>
       <c r="BU17" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BV17" t="s">
+        <v>113</v>
+      </c>
+      <c r="BW17" t="s">
+        <v>110</v>
+      </c>
+      <c r="BX17" t="s">
         <v>112</v>
-      </c>
-      <c r="BW17" t="s">
-        <v>109</v>
-      </c>
-      <c r="BX17" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="18" spans="1:76">
@@ -4668,7 +4671,7 @@
         <v>103</v>
       </c>
       <c r="C18" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D18" t="s">
         <v>103</v>
@@ -4686,25 +4689,25 @@
         <v>103</v>
       </c>
       <c r="I18" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J18" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K18" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L18" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M18" t="s">
         <v>103</v>
       </c>
       <c r="N18" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="O18" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="P18" t="s">
         <v>103</v>
@@ -4713,7 +4716,7 @@
         <v>103</v>
       </c>
       <c r="R18" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="S18" t="s">
         <v>103</v>
@@ -4722,7 +4725,7 @@
         <v>103</v>
       </c>
       <c r="U18" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="V18" t="s">
         <v>103</v>
@@ -4746,22 +4749,22 @@
         <v>103</v>
       </c>
       <c r="AC18" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AD18" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AE18" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AF18" t="s">
         <v>103</v>
       </c>
       <c r="AG18" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AH18" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AI18" t="s">
         <v>103</v>
@@ -4770,124 +4773,124 @@
         <v>103</v>
       </c>
       <c r="AK18" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AL18" t="s">
         <v>103</v>
       </c>
       <c r="AM18" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AN18" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AO18" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AP18" t="s">
         <v>103</v>
       </c>
       <c r="AQ18" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AR18" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AS18" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AT18" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AU18" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AV18" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AW18" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AX18" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AY18" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AZ18" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BA18" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BB18" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BC18" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BD18" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="BE18" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BF18" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BG18" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BH18" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BI18" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BJ18" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BK18" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BL18" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BM18" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BN18" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BO18" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BP18" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BQ18" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BR18" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BS18" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BT18" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BU18" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BV18" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="BW18" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="BX18" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="19" spans="1:76">
@@ -4895,7 +4898,7 @@
         <v>93</v>
       </c>
       <c r="B19" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C19" t="s">
         <v>103</v>
@@ -4904,7 +4907,7 @@
         <v>103</v>
       </c>
       <c r="E19" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F19" t="s">
         <v>103</v>
@@ -4916,16 +4919,16 @@
         <v>103</v>
       </c>
       <c r="I19" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J19" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K19" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L19" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M19" t="s">
         <v>103</v>
@@ -4937,52 +4940,52 @@
         <v>103</v>
       </c>
       <c r="P19" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Q19" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="R19" t="s">
         <v>103</v>
       </c>
       <c r="S19" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="T19" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="U19" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="V19" t="s">
         <v>103</v>
       </c>
       <c r="W19" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="X19" t="s">
         <v>103</v>
       </c>
       <c r="Y19" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Z19" t="s">
         <v>103</v>
       </c>
       <c r="AA19" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AB19" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AC19" t="s">
         <v>103</v>
       </c>
       <c r="AD19" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AE19" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AF19" t="s">
         <v>103</v>
@@ -4994,49 +4997,49 @@
         <v>103</v>
       </c>
       <c r="AI19" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AJ19" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK19" t="s">
         <v>103</v>
       </c>
       <c r="AL19" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AM19" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AN19" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AO19" t="s">
         <v>103</v>
       </c>
       <c r="AP19" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AQ19" t="s">
         <v>103</v>
       </c>
       <c r="AR19" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AS19" t="s">
         <v>103</v>
       </c>
       <c r="AT19" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AU19" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AV19" t="s">
         <v>103</v>
       </c>
       <c r="AW19" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AX19" t="s">
         <v>103</v>
@@ -5048,10 +5051,10 @@
         <v>103</v>
       </c>
       <c r="BA19" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BB19" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BC19" t="s">
         <v>103</v>
@@ -5069,25 +5072,25 @@
         <v>103</v>
       </c>
       <c r="BH19" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BI19" t="s">
+        <v>106</v>
+      </c>
+      <c r="BJ19" t="s">
         <v>105</v>
       </c>
-      <c r="BJ19" t="s">
-        <v>104</v>
-      </c>
       <c r="BK19" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="BL19" t="s">
         <v>103</v>
       </c>
       <c r="BM19" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="BN19" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="BO19" t="s">
         <v>103</v>
@@ -5105,19 +5108,19 @@
         <v>103</v>
       </c>
       <c r="BT19" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BU19" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BV19" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BW19" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="BX19" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="20" spans="1:76">
@@ -5125,142 +5128,142 @@
         <v>94</v>
       </c>
       <c r="B20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="O20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="P20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Q20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="R20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="S20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="T20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="U20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="V20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="W20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="X20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Y20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Z20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AA20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AB20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AC20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AD20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AE20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AF20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AG20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AH20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AI20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AJ20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AL20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AM20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AN20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AO20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AP20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AQ20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AR20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AS20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AT20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AU20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AV20" t="s">
         <v>103</v>
@@ -5272,22 +5275,22 @@
         <v>103</v>
       </c>
       <c r="AY20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AZ20" t="s">
         <v>103</v>
       </c>
       <c r="BA20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BB20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BC20" t="s">
         <v>103</v>
       </c>
       <c r="BD20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BE20" t="s">
         <v>103</v>
@@ -5299,16 +5302,16 @@
         <v>103</v>
       </c>
       <c r="BH20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BI20" t="s">
         <v>103</v>
       </c>
       <c r="BJ20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BK20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BL20" t="s">
         <v>103</v>
@@ -5317,37 +5320,37 @@
         <v>103</v>
       </c>
       <c r="BN20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BO20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BP20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BQ20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BR20" t="s">
         <v>103</v>
       </c>
       <c r="BS20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BT20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BU20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BV20" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="BW20" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="BX20" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="21" spans="1:76">
@@ -5355,13 +5358,13 @@
         <v>95</v>
       </c>
       <c r="B21" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C21" t="s">
         <v>103</v>
       </c>
       <c r="D21" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E21" t="s">
         <v>103</v>
@@ -5370,61 +5373,61 @@
         <v>103</v>
       </c>
       <c r="G21" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H21" t="s">
         <v>103</v>
       </c>
       <c r="I21" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J21" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K21" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L21" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M21" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N21" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="O21" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="P21" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Q21" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="R21" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="S21" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="T21" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="U21" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="V21" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="W21" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="X21" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Y21" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Z21" t="s">
         <v>103</v>
@@ -5436,10 +5439,10 @@
         <v>103</v>
       </c>
       <c r="AC21" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AD21" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AE21" t="s">
         <v>103</v>
@@ -5481,19 +5484,19 @@
         <v>103</v>
       </c>
       <c r="AR21" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AS21" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AT21" t="s">
         <v>103</v>
       </c>
       <c r="AU21" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AV21" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AW21" t="s">
         <v>103</v>
@@ -5502,82 +5505,82 @@
         <v>103</v>
       </c>
       <c r="AY21" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AZ21" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BA21" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BB21" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BC21" t="s">
         <v>103</v>
       </c>
       <c r="BD21" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BE21" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BF21" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BG21" t="s">
         <v>103</v>
       </c>
       <c r="BH21" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BI21" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BJ21" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BK21" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BL21" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="BM21" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BN21" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="BO21" t="s">
         <v>103</v>
       </c>
       <c r="BP21" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BQ21" t="s">
         <v>103</v>
       </c>
       <c r="BR21" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="BS21" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BT21" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BU21" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BV21" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="BW21" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="BX21" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="22" spans="1:76">
@@ -5585,13 +5588,13 @@
         <v>96</v>
       </c>
       <c r="B22" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C22" t="s">
         <v>103</v>
       </c>
       <c r="D22" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E22" t="s">
         <v>103</v>
@@ -5603,22 +5606,22 @@
         <v>103</v>
       </c>
       <c r="H22" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I22" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J22" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K22" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L22" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M22" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N22" t="s">
         <v>103</v>
@@ -5627,7 +5630,7 @@
         <v>103</v>
       </c>
       <c r="P22" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Q22" t="s">
         <v>103</v>
@@ -5642,13 +5645,13 @@
         <v>103</v>
       </c>
       <c r="U22" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="V22" t="s">
         <v>103</v>
       </c>
       <c r="W22" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="X22" t="s">
         <v>103</v>
@@ -5678,7 +5681,7 @@
         <v>103</v>
       </c>
       <c r="AG22" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AH22" t="s">
         <v>103</v>
@@ -5687,13 +5690,13 @@
         <v>103</v>
       </c>
       <c r="AJ22" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK22" t="s">
         <v>103</v>
       </c>
       <c r="AL22" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AM22" t="s">
         <v>103</v>
@@ -5705,7 +5708,7 @@
         <v>103</v>
       </c>
       <c r="AP22" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AQ22" t="s">
         <v>103</v>
@@ -5723,7 +5726,7 @@
         <v>103</v>
       </c>
       <c r="AV22" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AW22" t="s">
         <v>103</v>
@@ -5738,22 +5741,22 @@
         <v>103</v>
       </c>
       <c r="BA22" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BB22" t="s">
+        <v>106</v>
+      </c>
+      <c r="BC22" t="s">
+        <v>104</v>
+      </c>
+      <c r="BD22" t="s">
         <v>105</v>
       </c>
-      <c r="BC22" t="s">
-        <v>103</v>
-      </c>
-      <c r="BD22" t="s">
-        <v>104</v>
-      </c>
       <c r="BE22" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BF22" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BG22" t="s">
         <v>103</v>
@@ -5762,52 +5765,52 @@
         <v>103</v>
       </c>
       <c r="BI22" t="s">
+        <v>106</v>
+      </c>
+      <c r="BJ22" t="s">
+        <v>106</v>
+      </c>
+      <c r="BK22" t="s">
+        <v>106</v>
+      </c>
+      <c r="BL22" t="s">
         <v>105</v>
       </c>
-      <c r="BJ22" t="s">
+      <c r="BM22" t="s">
+        <v>106</v>
+      </c>
+      <c r="BN22" t="s">
+        <v>104</v>
+      </c>
+      <c r="BO22" t="s">
+        <v>104</v>
+      </c>
+      <c r="BP22" t="s">
         <v>105</v>
       </c>
-      <c r="BK22" t="s">
+      <c r="BQ22" t="s">
+        <v>103</v>
+      </c>
+      <c r="BR22" t="s">
+        <v>106</v>
+      </c>
+      <c r="BS22" t="s">
+        <v>103</v>
+      </c>
+      <c r="BT22" t="s">
+        <v>103</v>
+      </c>
+      <c r="BU22" t="s">
         <v>105</v>
       </c>
-      <c r="BL22" t="s">
-        <v>104</v>
-      </c>
-      <c r="BM22" t="s">
-        <v>105</v>
-      </c>
-      <c r="BN22" t="s">
-        <v>103</v>
-      </c>
-      <c r="BO22" t="s">
-        <v>103</v>
-      </c>
-      <c r="BP22" t="s">
-        <v>104</v>
-      </c>
-      <c r="BQ22" t="s">
-        <v>103</v>
-      </c>
-      <c r="BR22" t="s">
-        <v>105</v>
-      </c>
-      <c r="BS22" t="s">
-        <v>103</v>
-      </c>
-      <c r="BT22" t="s">
-        <v>103</v>
-      </c>
-      <c r="BU22" t="s">
-        <v>104</v>
-      </c>
       <c r="BV22" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="BW22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BX22" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="23" spans="1:76">
@@ -5815,46 +5818,46 @@
         <v>97</v>
       </c>
       <c r="B23" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C23" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D23" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E23" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F23" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G23" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H23" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I23" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J23" t="s">
         <v>103</v>
       </c>
       <c r="K23" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L23" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M23" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N23" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="O23" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="P23" t="s">
         <v>103</v>
@@ -5863,10 +5866,10 @@
         <v>103</v>
       </c>
       <c r="R23" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="S23" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="T23" t="s">
         <v>103</v>
@@ -5875,13 +5878,13 @@
         <v>103</v>
       </c>
       <c r="V23" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="W23" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="X23" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Y23" t="s">
         <v>103</v>
@@ -5890,13 +5893,13 @@
         <v>103</v>
       </c>
       <c r="AA23" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AB23" t="s">
         <v>103</v>
       </c>
       <c r="AC23" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AD23" t="s">
         <v>103</v>
@@ -5908,7 +5911,7 @@
         <v>103</v>
       </c>
       <c r="AG23" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AH23" t="s">
         <v>103</v>
@@ -5917,19 +5920,19 @@
         <v>103</v>
       </c>
       <c r="AJ23" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK23" t="s">
         <v>103</v>
       </c>
       <c r="AL23" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AM23" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AN23" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AO23" t="s">
         <v>103</v>
@@ -5938,88 +5941,88 @@
         <v>103</v>
       </c>
       <c r="AQ23" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AR23" t="s">
         <v>103</v>
       </c>
       <c r="AS23" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AT23" t="s">
         <v>103</v>
       </c>
       <c r="AU23" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AV23" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AW23" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AX23" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AY23" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AZ23" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BA23" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BB23" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BC23" t="s">
         <v>103</v>
       </c>
       <c r="BD23" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BE23" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BF23" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="BG23" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BH23" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BI23" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BJ23" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BK23" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BL23" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BM23" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="BN23" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="BO23" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BP23" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BQ23" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BR23" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BS23" t="s">
         <v>103</v>
@@ -6028,16 +6031,16 @@
         <v>103</v>
       </c>
       <c r="BU23" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BV23" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="BW23" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="BX23" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="24" spans="1:76">
@@ -6045,151 +6048,151 @@
         <v>98</v>
       </c>
       <c r="B24" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C24" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D24" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E24" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F24" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G24" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H24" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I24" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J24" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K24" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L24" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M24" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N24" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="O24" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="P24" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Q24" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="R24" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="S24" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="T24" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="U24" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="V24" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="W24" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="X24" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Y24" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Z24" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AA24" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AB24" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AC24" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AD24" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AE24" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AF24" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AG24" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AH24" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AI24" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AJ24" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK24" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AL24" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AM24" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AN24" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AO24" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AP24" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AQ24" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AR24" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AS24" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AT24" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AU24" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AV24" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AW24" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AX24" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AY24" t="s">
         <v>103</v>
@@ -6204,34 +6207,34 @@
         <v>103</v>
       </c>
       <c r="BC24" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BD24" t="s">
         <v>103</v>
       </c>
       <c r="BE24" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BF24" t="s">
         <v>103</v>
       </c>
       <c r="BG24" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BH24" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BI24" t="s">
         <v>103</v>
       </c>
       <c r="BJ24" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BK24" t="s">
         <v>103</v>
       </c>
       <c r="BL24" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BM24" t="s">
         <v>103</v>
@@ -6246,7 +6249,7 @@
         <v>103</v>
       </c>
       <c r="BQ24" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BR24" t="s">
         <v>103</v>
@@ -6255,19 +6258,19 @@
         <v>103</v>
       </c>
       <c r="BT24" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BU24" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BV24" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="BW24" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="BX24" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="25" spans="1:76">
@@ -6275,136 +6278,136 @@
         <v>99</v>
       </c>
       <c r="B25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="O25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="P25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Q25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="R25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="S25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="T25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="U25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="V25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="W25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="X25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Y25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Z25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AA25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AB25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AC25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AD25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AE25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AF25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AG25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AH25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AI25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AJ25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AL25" t="s">
         <v>103</v>
       </c>
       <c r="AM25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AN25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AO25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AP25" t="s">
         <v>103</v>
       </c>
       <c r="AQ25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AR25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AS25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AT25" t="s">
         <v>103</v>
@@ -6416,43 +6419,43 @@
         <v>103</v>
       </c>
       <c r="AW25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AX25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AY25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AZ25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BA25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BB25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BC25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BD25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BE25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BF25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BG25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BH25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BI25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BJ25" t="s">
         <v>103</v>
@@ -6461,10 +6464,10 @@
         <v>103</v>
       </c>
       <c r="BL25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BM25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BN25" t="s">
         <v>103</v>
@@ -6473,31 +6476,31 @@
         <v>103</v>
       </c>
       <c r="BP25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BQ25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BR25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BS25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BT25" t="s">
         <v>103</v>
       </c>
       <c r="BU25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BV25" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="BW25" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="BX25" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="26" spans="1:76">
@@ -6505,91 +6508,91 @@
         <v>100</v>
       </c>
       <c r="B26" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C26" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D26" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E26" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F26" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G26" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H26" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I26" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J26" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K26" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L26" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M26" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N26" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="O26" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="P26" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Q26" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="R26" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="S26" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="T26" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="U26" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="V26" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="W26" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="X26" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Y26" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Z26" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AA26" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AB26" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AC26" t="s">
         <v>103</v>
       </c>
       <c r="AD26" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AE26" t="s">
         <v>103</v>
@@ -6601,55 +6604,55 @@
         <v>103</v>
       </c>
       <c r="AH26" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AI26" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AJ26" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK26" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AL26" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AM26" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AN26" t="s">
         <v>103</v>
       </c>
       <c r="AO26" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AP26" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AQ26" t="s">
         <v>103</v>
       </c>
       <c r="AR26" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AS26" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AT26" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AU26" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AV26" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AW26" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AX26" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AY26" t="s">
         <v>103</v>
@@ -6664,25 +6667,25 @@
         <v>103</v>
       </c>
       <c r="BC26" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BD26" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BE26" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BF26" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BG26" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BH26" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BI26" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BJ26" t="s">
         <v>103</v>
@@ -6691,7 +6694,7 @@
         <v>103</v>
       </c>
       <c r="BL26" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="BM26" t="s">
         <v>103</v>
@@ -6700,7 +6703,7 @@
         <v>103</v>
       </c>
       <c r="BO26" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="BP26" t="s">
         <v>103</v>
@@ -6712,22 +6715,22 @@
         <v>103</v>
       </c>
       <c r="BS26" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BT26" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BU26" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BV26" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="BW26" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="BX26" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="27" spans="1:76">
@@ -6735,7 +6738,7 @@
         <v>101</v>
       </c>
       <c r="B27" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C27" t="s">
         <v>103</v>
@@ -6744,10 +6747,10 @@
         <v>103</v>
       </c>
       <c r="E27" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F27" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G27" t="s">
         <v>103</v>
@@ -6756,64 +6759,64 @@
         <v>103</v>
       </c>
       <c r="I27" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J27" t="s">
         <v>103</v>
       </c>
       <c r="K27" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L27" t="s">
         <v>103</v>
       </c>
       <c r="M27" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N27" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="O27" t="s">
         <v>103</v>
       </c>
       <c r="P27" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Q27" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="R27" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="S27" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="T27" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="U27" t="s">
         <v>103</v>
       </c>
       <c r="V27" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="W27" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="X27" t="s">
         <v>103</v>
       </c>
       <c r="Y27" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Z27" t="s">
         <v>103</v>
       </c>
       <c r="AA27" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AB27" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AC27" t="s">
         <v>103</v>
@@ -6825,91 +6828,91 @@
         <v>103</v>
       </c>
       <c r="AF27" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AG27" t="s">
         <v>103</v>
       </c>
       <c r="AH27" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AI27" t="s">
         <v>103</v>
       </c>
       <c r="AJ27" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK27" t="s">
         <v>103</v>
       </c>
       <c r="AL27" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AM27" t="s">
         <v>103</v>
       </c>
       <c r="AN27" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AO27" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AP27" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AQ27" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AR27" t="s">
         <v>103</v>
       </c>
       <c r="AS27" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AT27" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AU27" t="s">
         <v>103</v>
       </c>
       <c r="AV27" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AW27" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AX27" t="s">
         <v>103</v>
       </c>
       <c r="AY27" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AZ27" t="s">
         <v>103</v>
       </c>
       <c r="BA27" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BB27" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BC27" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BD27" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="BE27" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BF27" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BG27" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BH27" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="BI27" t="s">
         <v>103</v>
@@ -6918,7 +6921,7 @@
         <v>103</v>
       </c>
       <c r="BK27" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="BL27" t="s">
         <v>103</v>
@@ -6930,34 +6933,34 @@
         <v>103</v>
       </c>
       <c r="BO27" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BP27" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BQ27" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="BR27" t="s">
         <v>103</v>
       </c>
       <c r="BS27" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BT27" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BU27" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BV27" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="BW27" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="BX27" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="28" spans="1:76">
@@ -6965,43 +6968,43 @@
         <v>102</v>
       </c>
       <c r="B28" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C28" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D28" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E28" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F28" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G28" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H28" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I28" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J28" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K28" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L28" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M28" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N28" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="O28" t="s">
         <v>103</v>
@@ -7028,7 +7031,7 @@
         <v>103</v>
       </c>
       <c r="W28" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="X28" t="s">
         <v>103</v>
@@ -7076,118 +7079,118 @@
         <v>103</v>
       </c>
       <c r="AM28" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AN28" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AO28" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AP28" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AQ28" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AR28" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AS28" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AT28" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AU28" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AV28" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AW28" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AX28" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AY28" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AZ28" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BA28" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BB28" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BC28" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BD28" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BE28" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BF28" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BG28" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BH28" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BI28" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BJ28" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BK28" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BL28" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="BM28" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="BN28" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="BO28" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="BP28" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BQ28" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BR28" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BS28" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BT28" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="BU28" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="BV28" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="BW28" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="BX28" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/Beans_(fava,_dry)_percentile_classification_matrix.xlsx
+++ b/outputs/Beans_(fava,_dry)_percentile_classification_matrix.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2128" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2128" uniqueCount="106">
   <si>
     <t>2020 Mar</t>
   </si>
@@ -331,46 +331,7 @@
     <t>No data</t>
   </si>
   <si>
-    <t>Alert</t>
-  </si>
-  <si>
-    <t>Alarm</t>
-  </si>
-  <si>
     <t>0%</t>
-  </si>
-  <si>
-    <t>11%</t>
-  </si>
-  <si>
-    <t>6%</t>
-  </si>
-  <si>
-    <t>3%</t>
-  </si>
-  <si>
-    <t>14%</t>
-  </si>
-  <si>
-    <t>7%</t>
-  </si>
-  <si>
-    <t>4%</t>
-  </si>
-  <si>
-    <t>8%</t>
-  </si>
-  <si>
-    <t>1%</t>
-  </si>
-  <si>
-    <t>10%</t>
-  </si>
-  <si>
-    <t>19%</t>
-  </si>
-  <si>
-    <t>18%</t>
   </si>
 </sst>
 </file>
@@ -997,7 +958,7 @@
         <v>104</v>
       </c>
       <c r="E2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F2" t="s">
         <v>103</v>
@@ -1027,10 +988,10 @@
         <v>103</v>
       </c>
       <c r="O2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="P2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Q2" t="s">
         <v>104</v>
@@ -1042,22 +1003,22 @@
         <v>103</v>
       </c>
       <c r="T2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="U2" t="s">
         <v>103</v>
       </c>
       <c r="V2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="W2" t="s">
         <v>104</v>
       </c>
       <c r="X2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Y2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Z2" t="s">
         <v>104</v>
@@ -1204,13 +1165,13 @@
         <v>104</v>
       </c>
       <c r="BV2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="BW2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="BX2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="3" spans="1:76">
@@ -1368,10 +1329,10 @@
         <v>104</v>
       </c>
       <c r="AZ3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BA3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BB3" t="s">
         <v>104</v>
@@ -1419,7 +1380,7 @@
         <v>104</v>
       </c>
       <c r="BQ3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BR3" t="s">
         <v>104</v>
@@ -1434,13 +1395,13 @@
         <v>104</v>
       </c>
       <c r="BV3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="BW3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="BX3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="4" spans="1:76">
@@ -1598,7 +1559,7 @@
         <v>103</v>
       </c>
       <c r="AZ4" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="BA4" t="s">
         <v>104</v>
@@ -1610,16 +1571,16 @@
         <v>103</v>
       </c>
       <c r="BD4" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="BE4" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="BF4" t="s">
         <v>104</v>
       </c>
       <c r="BG4" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="BH4" t="s">
         <v>104</v>
@@ -1637,19 +1598,19 @@
         <v>104</v>
       </c>
       <c r="BM4" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="BN4" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="BO4" t="s">
         <v>103</v>
       </c>
       <c r="BP4" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="BQ4" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="BR4" t="s">
         <v>104</v>
@@ -1658,19 +1619,19 @@
         <v>104</v>
       </c>
       <c r="BT4" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="BU4" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="BV4" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="BW4" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="BX4" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
     </row>
     <row r="5" spans="1:76">
@@ -1840,7 +1801,7 @@
         <v>103</v>
       </c>
       <c r="BD5" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="BE5" t="s">
         <v>103</v>
@@ -1849,22 +1810,22 @@
         <v>103</v>
       </c>
       <c r="BG5" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="BH5" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="BI5" t="s">
         <v>103</v>
       </c>
       <c r="BJ5" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="BK5" t="s">
         <v>104</v>
       </c>
       <c r="BL5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BM5" t="s">
         <v>103</v>
@@ -1876,7 +1837,7 @@
         <v>103</v>
       </c>
       <c r="BP5" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="BQ5" t="s">
         <v>103</v>
@@ -1885,7 +1846,7 @@
         <v>103</v>
       </c>
       <c r="BS5" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="BT5" t="s">
         <v>104</v>
@@ -1894,13 +1855,13 @@
         <v>104</v>
       </c>
       <c r="BV5" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="BW5" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="BX5" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
     </row>
     <row r="6" spans="1:76">
@@ -2040,7 +2001,7 @@
         <v>103</v>
       </c>
       <c r="AT6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AU6" t="s">
         <v>104</v>
@@ -2052,10 +2013,10 @@
         <v>103</v>
       </c>
       <c r="AX6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AY6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AZ6" t="s">
         <v>103</v>
@@ -2064,28 +2025,28 @@
         <v>103</v>
       </c>
       <c r="BB6" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="BC6" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="BD6" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="BE6" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="BF6" t="s">
         <v>104</v>
       </c>
       <c r="BG6" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="BH6" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="BI6" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="BJ6" t="s">
         <v>104</v>
@@ -2124,13 +2085,13 @@
         <v>104</v>
       </c>
       <c r="BV6" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="BW6" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c r="BX6" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
     </row>
     <row r="7" spans="1:76">
@@ -2336,10 +2297,10 @@
         <v>104</v>
       </c>
       <c r="BP7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BQ7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BR7" t="s">
         <v>104</v>
@@ -2354,13 +2315,13 @@
         <v>104</v>
       </c>
       <c r="BV7" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="BW7" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="BX7" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="8" spans="1:76">
@@ -2437,7 +2398,7 @@
         <v>103</v>
       </c>
       <c r="Y8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Z8" t="s">
         <v>104</v>
@@ -2452,7 +2413,7 @@
         <v>103</v>
       </c>
       <c r="AD8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AE8" t="s">
         <v>104</v>
@@ -2533,7 +2494,7 @@
         <v>104</v>
       </c>
       <c r="BE8" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="BF8" t="s">
         <v>103</v>
@@ -2584,13 +2545,13 @@
         <v>104</v>
       </c>
       <c r="BV8" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="BW8" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="BX8" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
     </row>
     <row r="9" spans="1:76">
@@ -2625,16 +2586,16 @@
         <v>103</v>
       </c>
       <c r="K9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M9" t="s">
         <v>103</v>
       </c>
       <c r="N9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="O9" t="s">
         <v>103</v>
@@ -2643,7 +2604,7 @@
         <v>104</v>
       </c>
       <c r="Q9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="R9" t="s">
         <v>104</v>
@@ -2655,7 +2616,7 @@
         <v>103</v>
       </c>
       <c r="U9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="V9" t="s">
         <v>103</v>
@@ -2676,7 +2637,7 @@
         <v>103</v>
       </c>
       <c r="AB9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AC9" t="s">
         <v>104</v>
@@ -2814,13 +2775,13 @@
         <v>104</v>
       </c>
       <c r="BV9" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="BW9" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="BX9" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="10" spans="1:76">
@@ -2942,25 +2903,25 @@
         <v>104</v>
       </c>
       <c r="AN10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AO10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AP10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AQ10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AR10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AS10" t="s">
         <v>103</v>
       </c>
       <c r="AT10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AU10" t="s">
         <v>104</v>
@@ -3038,19 +2999,19 @@
         <v>104</v>
       </c>
       <c r="BT10" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="BU10" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="BV10" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="BW10" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="BX10" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
     </row>
     <row r="11" spans="1:76">
@@ -3259,10 +3220,10 @@
         <v>104</v>
       </c>
       <c r="BQ11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BR11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BS11" t="s">
         <v>104</v>
@@ -3274,13 +3235,13 @@
         <v>104</v>
       </c>
       <c r="BV11" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="BW11" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="BX11" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="12" spans="1:76">
@@ -3426,7 +3387,7 @@
         <v>104</v>
       </c>
       <c r="AV12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AW12" t="s">
         <v>104</v>
@@ -3444,7 +3405,7 @@
         <v>104</v>
       </c>
       <c r="BB12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BC12" t="s">
         <v>104</v>
@@ -3483,7 +3444,7 @@
         <v>104</v>
       </c>
       <c r="BO12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BP12" t="s">
         <v>104</v>
@@ -3504,13 +3465,13 @@
         <v>104</v>
       </c>
       <c r="BV12" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="BW12" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="BX12" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="13" spans="1:76">
@@ -3668,61 +3629,61 @@
         <v>103</v>
       </c>
       <c r="AZ13" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="BA13" t="s">
         <v>104</v>
       </c>
       <c r="BB13" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="BC13" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="BD13" t="s">
         <v>104</v>
       </c>
       <c r="BE13" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="BF13" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="BG13" t="s">
         <v>104</v>
       </c>
       <c r="BH13" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="BI13" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="BJ13" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="BK13" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="BL13" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="BM13" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="BN13" t="s">
         <v>104</v>
       </c>
       <c r="BO13" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="BP13" t="s">
         <v>104</v>
       </c>
       <c r="BQ13" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="BR13" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="BS13" t="s">
         <v>103</v>
@@ -3734,13 +3695,13 @@
         <v>104</v>
       </c>
       <c r="BV13" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="BW13" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="BX13" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
     </row>
     <row r="14" spans="1:76">
@@ -3895,7 +3856,7 @@
         <v>103</v>
       </c>
       <c r="AY14" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="AZ14" t="s">
         <v>103</v>
@@ -3904,13 +3865,13 @@
         <v>103</v>
       </c>
       <c r="BB14" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="BC14" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="BD14" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="BE14" t="s">
         <v>103</v>
@@ -3922,7 +3883,7 @@
         <v>104</v>
       </c>
       <c r="BH14" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="BI14" t="s">
         <v>103</v>
@@ -3931,46 +3892,46 @@
         <v>103</v>
       </c>
       <c r="BK14" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="BL14" t="s">
         <v>103</v>
       </c>
       <c r="BM14" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="BN14" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="BO14" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="BP14" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="BQ14" t="s">
         <v>103</v>
       </c>
       <c r="BR14" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="BS14" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="BT14" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="BU14" t="s">
         <v>103</v>
       </c>
       <c r="BV14" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="BW14" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="BX14" t="s">
-        <v>118</v>
+        <v>105</v>
       </c>
     </row>
     <row r="15" spans="1:76">
@@ -4002,7 +3963,7 @@
         <v>104</v>
       </c>
       <c r="J15" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K15" t="s">
         <v>103</v>
@@ -4086,7 +4047,7 @@
         <v>103</v>
       </c>
       <c r="AL15" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AM15" t="s">
         <v>104</v>
@@ -4119,7 +4080,7 @@
         <v>104</v>
       </c>
       <c r="AW15" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="AX15" t="s">
         <v>104</v>
@@ -4179,7 +4140,7 @@
         <v>103</v>
       </c>
       <c r="BQ15" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BR15" t="s">
         <v>104</v>
@@ -4194,13 +4155,13 @@
         <v>104</v>
       </c>
       <c r="BV15" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="BW15" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="BX15" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
     </row>
     <row r="16" spans="1:76">
@@ -4217,10 +4178,10 @@
         <v>103</v>
       </c>
       <c r="E16" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F16" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G16" t="s">
         <v>104</v>
@@ -4370,16 +4331,16 @@
         <v>103</v>
       </c>
       <c r="BD16" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="BE16" t="s">
         <v>103</v>
       </c>
       <c r="BF16" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="BG16" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="BH16" t="s">
         <v>104</v>
@@ -4391,10 +4352,10 @@
         <v>104</v>
       </c>
       <c r="BK16" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="BL16" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="BM16" t="s">
         <v>104</v>
@@ -4403,7 +4364,7 @@
         <v>104</v>
       </c>
       <c r="BO16" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="BP16" t="s">
         <v>104</v>
@@ -4415,7 +4376,7 @@
         <v>104</v>
       </c>
       <c r="BS16" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="BT16" t="s">
         <v>104</v>
@@ -4424,13 +4385,13 @@
         <v>104</v>
       </c>
       <c r="BV16" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="BW16" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="BX16" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
     </row>
     <row r="17" spans="1:76">
@@ -4606,10 +4567,10 @@
         <v>103</v>
       </c>
       <c r="BF17" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="BG17" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="BH17" t="s">
         <v>104</v>
@@ -4618,16 +4579,16 @@
         <v>103</v>
       </c>
       <c r="BJ17" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="BK17" t="s">
         <v>104</v>
       </c>
       <c r="BL17" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BM17" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="BN17" t="s">
         <v>104</v>
@@ -4645,7 +4606,7 @@
         <v>104</v>
       </c>
       <c r="BS17" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="BT17" t="s">
         <v>103</v>
@@ -4654,13 +4615,13 @@
         <v>104</v>
       </c>
       <c r="BV17" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="BW17" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="BX17" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
     </row>
     <row r="18" spans="1:76">
@@ -4728,7 +4689,7 @@
         <v>104</v>
       </c>
       <c r="V18" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="W18" t="s">
         <v>103</v>
@@ -4743,7 +4704,7 @@
         <v>103</v>
       </c>
       <c r="AA18" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AB18" t="s">
         <v>103</v>
@@ -4830,7 +4791,7 @@
         <v>104</v>
       </c>
       <c r="BD18" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="BE18" t="s">
         <v>104</v>
@@ -4884,13 +4845,13 @@
         <v>104</v>
       </c>
       <c r="BV18" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="BW18" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="BX18" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
     </row>
     <row r="19" spans="1:76">
@@ -5075,22 +5036,22 @@
         <v>104</v>
       </c>
       <c r="BI19" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="BJ19" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="BK19" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="BL19" t="s">
         <v>103</v>
       </c>
       <c r="BM19" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="BN19" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="BO19" t="s">
         <v>103</v>
@@ -5114,13 +5075,13 @@
         <v>104</v>
       </c>
       <c r="BV19" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="BW19" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="BX19" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
     </row>
     <row r="20" spans="1:76">
@@ -5266,13 +5227,13 @@
         <v>104</v>
       </c>
       <c r="AV20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AW20" t="s">
         <v>103</v>
       </c>
       <c r="AX20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AY20" t="s">
         <v>104</v>
@@ -5287,19 +5248,19 @@
         <v>104</v>
       </c>
       <c r="BC20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BD20" t="s">
         <v>104</v>
       </c>
       <c r="BE20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BF20" t="s">
         <v>103</v>
       </c>
       <c r="BG20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BH20" t="s">
         <v>104</v>
@@ -5317,7 +5278,7 @@
         <v>103</v>
       </c>
       <c r="BM20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BN20" t="s">
         <v>104</v>
@@ -5344,13 +5305,13 @@
         <v>104</v>
       </c>
       <c r="BV20" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="BW20" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="BX20" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="21" spans="1:76">
@@ -5460,7 +5421,7 @@
         <v>103</v>
       </c>
       <c r="AJ21" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK21" t="s">
         <v>103</v>
@@ -5544,13 +5505,13 @@
         <v>104</v>
       </c>
       <c r="BL21" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="BM21" t="s">
         <v>104</v>
       </c>
       <c r="BN21" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="BO21" t="s">
         <v>103</v>
@@ -5562,7 +5523,7 @@
         <v>103</v>
       </c>
       <c r="BR21" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="BS21" t="s">
         <v>104</v>
@@ -5574,13 +5535,13 @@
         <v>104</v>
       </c>
       <c r="BV21" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="BW21" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="BX21" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
     </row>
     <row r="22" spans="1:76">
@@ -5744,13 +5705,13 @@
         <v>104</v>
       </c>
       <c r="BB22" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="BC22" t="s">
         <v>104</v>
       </c>
       <c r="BD22" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="BE22" t="s">
         <v>104</v>
@@ -5765,19 +5726,19 @@
         <v>103</v>
       </c>
       <c r="BI22" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="BJ22" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="BK22" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="BL22" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="BM22" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="BN22" t="s">
         <v>104</v>
@@ -5786,13 +5747,13 @@
         <v>104</v>
       </c>
       <c r="BP22" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="BQ22" t="s">
         <v>103</v>
       </c>
       <c r="BR22" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="BS22" t="s">
         <v>103</v>
@@ -5801,16 +5762,16 @@
         <v>103</v>
       </c>
       <c r="BU22" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="BV22" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="BW22" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="BX22" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
     </row>
     <row r="23" spans="1:76">
@@ -5875,7 +5836,7 @@
         <v>103</v>
       </c>
       <c r="U23" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="V23" t="s">
         <v>104</v>
@@ -5890,7 +5851,7 @@
         <v>103</v>
       </c>
       <c r="Z23" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AA23" t="s">
         <v>104</v>
@@ -5986,7 +5947,7 @@
         <v>104</v>
       </c>
       <c r="BF23" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="BG23" t="s">
         <v>104</v>
@@ -6007,10 +5968,10 @@
         <v>104</v>
       </c>
       <c r="BM23" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="BN23" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="BO23" t="s">
         <v>104</v>
@@ -6028,19 +5989,19 @@
         <v>103</v>
       </c>
       <c r="BT23" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BU23" t="s">
         <v>104</v>
       </c>
       <c r="BV23" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="BW23" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="BX23" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
     </row>
     <row r="24" spans="1:76">
@@ -6198,7 +6159,7 @@
         <v>103</v>
       </c>
       <c r="AZ24" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BA24" t="s">
         <v>103</v>
@@ -6225,7 +6186,7 @@
         <v>104</v>
       </c>
       <c r="BI24" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BJ24" t="s">
         <v>104</v>
@@ -6243,7 +6204,7 @@
         <v>103</v>
       </c>
       <c r="BO24" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BP24" t="s">
         <v>103</v>
@@ -6255,7 +6216,7 @@
         <v>103</v>
       </c>
       <c r="BS24" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BT24" t="s">
         <v>104</v>
@@ -6264,13 +6225,13 @@
         <v>104</v>
       </c>
       <c r="BV24" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="BW24" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="BX24" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="25" spans="1:76">
@@ -6410,10 +6371,10 @@
         <v>104</v>
       </c>
       <c r="AT25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AU25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AV25" t="s">
         <v>103</v>
@@ -6461,7 +6422,7 @@
         <v>103</v>
       </c>
       <c r="BK25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BL25" t="s">
         <v>104</v>
@@ -6473,7 +6434,7 @@
         <v>103</v>
       </c>
       <c r="BO25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BP25" t="s">
         <v>104</v>
@@ -6494,13 +6455,13 @@
         <v>104</v>
       </c>
       <c r="BV25" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="BW25" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="BX25" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="26" spans="1:76">
@@ -6688,13 +6649,13 @@
         <v>104</v>
       </c>
       <c r="BJ26" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BK26" t="s">
         <v>103</v>
       </c>
       <c r="BL26" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="BM26" t="s">
         <v>103</v>
@@ -6703,7 +6664,7 @@
         <v>103</v>
       </c>
       <c r="BO26" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="BP26" t="s">
         <v>103</v>
@@ -6712,7 +6673,7 @@
         <v>103</v>
       </c>
       <c r="BR26" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BS26" t="s">
         <v>104</v>
@@ -6724,13 +6685,13 @@
         <v>104</v>
       </c>
       <c r="BV26" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="BW26" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="BX26" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
     </row>
     <row r="27" spans="1:76">
@@ -6900,7 +6861,7 @@
         <v>104</v>
       </c>
       <c r="BD27" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="BE27" t="s">
         <v>104</v>
@@ -6912,7 +6873,7 @@
         <v>104</v>
       </c>
       <c r="BH27" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="BI27" t="s">
         <v>103</v>
@@ -6921,7 +6882,7 @@
         <v>103</v>
       </c>
       <c r="BK27" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="BL27" t="s">
         <v>103</v>
@@ -6939,7 +6900,7 @@
         <v>104</v>
       </c>
       <c r="BQ27" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="BR27" t="s">
         <v>103</v>
@@ -6954,13 +6915,13 @@
         <v>104</v>
       </c>
       <c r="BV27" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="BW27" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="BX27" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
     </row>
     <row r="28" spans="1:76">
@@ -7067,7 +7028,7 @@
         <v>103</v>
       </c>
       <c r="AI28" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AJ28" t="s">
         <v>103</v>
@@ -7079,7 +7040,7 @@
         <v>103</v>
       </c>
       <c r="AM28" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="AN28" t="s">
         <v>104</v>
@@ -7154,16 +7115,16 @@
         <v>104</v>
       </c>
       <c r="BL28" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="BM28" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="BN28" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="BO28" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="BP28" t="s">
         <v>104</v>
@@ -7178,19 +7139,19 @@
         <v>104</v>
       </c>
       <c r="BT28" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="BU28" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="BV28" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="BW28" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="BX28" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/Beans_(fava,_dry)_percentile_classification_matrix.xlsx
+++ b/outputs/Beans_(fava,_dry)_percentile_classification_matrix.xlsx
@@ -325,7 +325,7 @@
     <t>Yambio</t>
   </si>
   <si>
-    <t>Minimal</t>
+    <t>No concern</t>
   </si>
   <si>
     <t>No data</t>
